--- a/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
+++ b/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="95">
   <si>
     <t>CORE-ID</t>
   </si>
@@ -271,6 +271,15 @@
   </si>
   <si>
     <t>999</t>
+  </si>
+  <si>
+    <t>Executed</t>
+  </si>
+  <si>
+    <t>Skipped</t>
+  </si>
+  <si>
+    <t>Errored</t>
   </si>
   <si>
     <t>CG0001</t>
@@ -2392,7 +2401,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:G197"/>
+  <dimension ref="A1:I197"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="4" width="19.109375"/>
@@ -2401,7 +2410,9 @@
     <col min="4" max="4" customWidth="true" width="16.44140625"/>
     <col min="5" max="5" customWidth="true" style="4" width="103.44140625"/>
     <col min="6" max="6" customWidth="true" style="4" width="21.109375"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="26.88671875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="8" max="8" width="12.0" customWidth="true"/>
+    <col min="9" max="9" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2423,7 +2434,15 @@
       <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3"/>
+      <c r="G1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -2433,15 +2452,18 @@
         <v>69</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16" t="s">
         <v>63</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>81</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
@@ -2451,35 +2473,41 @@
         <v>73</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>66</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>81</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+      <c r="I3" s="15"/>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>69</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>87</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
@@ -3093,24 +3121,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
+++ b/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="97">
   <si>
     <t>CORE-ID</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>Library Metadata Basis</t>
+  </si>
+  <si>
+    <t>CT Declaration Mismatch</t>
+  </si>
+  <si>
+    <t>Define Metadata Basis</t>
   </si>
   <si>
     <t>2026-08-12T09:15:00</t>
@@ -814,7 +820,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="27.109375"/>
@@ -832,7 +838,7 @@
         <v>21</v>
       </c>
       <c r="B2" t="s" s="8">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -840,7 +846,7 @@
         <v>22</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -848,7 +854,7 @@
         <v>23</v>
       </c>
       <c r="B4" t="s" s="8">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -872,7 +878,7 @@
         <v>27</v>
       </c>
       <c r="B7" t="s" s="8">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -886,7 +892,7 @@
         <v>29</v>
       </c>
       <c r="B9" t="s" s="8">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -902,7 +908,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s" s="8">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -918,7 +924,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -926,7 +932,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -996,6 +1002,18 @@
         <v>44</v>
       </c>
       <c r="B23" s="9"/>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="9"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1049,16 +1067,16 @@
     </row>
     <row r="2" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E2" s="14" t="n">
         <v>12.5</v>
@@ -1069,16 +1087,16 @@
     </row>
     <row r="3" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E3" s="14" t="n">
         <v>3.25</v>
@@ -1295,13 +1313,13 @@
     </row>
     <row r="2" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B2" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="15" t="n">
         <v>2.0</v>
@@ -1309,13 +1327,13 @@
     </row>
     <row r="3" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" s="15" t="n">
         <v>1.0</v>
@@ -1589,87 +1607,87 @@
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F2" s="17" t="n">
         <v>3.0</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F3" s="17" t="n">
         <v>9.0</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I3" s="14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F4" s="17" t="n">
         <v>1.0</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="I4" s="14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -2435,31 +2453,31 @@
         <v>5</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
@@ -2467,22 +2485,22 @@
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>86</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>84</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
@@ -2490,20 +2508,20 @@
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
@@ -3121,24 +3139,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
+++ b/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="97">
   <si>
     <t>CORE-ID</t>
   </si>
@@ -240,6 +240,9 @@
     <t>AGE out of range</t>
   </si>
   <si>
+    <t>Columns (name only)</t>
+  </si>
+  <si>
     <t>fully executable</t>
   </si>
   <si>
@@ -259,9 +262,6 @@
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>AESTDY</t>
   </si>
   <si>
     <t/>
@@ -1562,7 +1562,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="4" width="19.109375"/>
@@ -1574,6 +1574,7 @@
     <col min="7" max="7" bestFit="true" customWidth="true" width="12.0"/>
     <col min="8" max="8" bestFit="true" customWidth="true" style="4" width="35.44140625"/>
     <col min="9" max="9" bestFit="true" customWidth="true" style="4" width="64.44140625"/>
+    <col min="10" max="10" width="24.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1604,6 +1605,9 @@
       <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="2" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -1613,26 +1617,27 @@
         <v>65</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D2" s="15" t="s">
         <v>55</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" s="17" t="n">
         <v>3.0</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H2" s="16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" s="14" t="s">
-        <v>73</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
@@ -1642,26 +1647,27 @@
         <v>65</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>55</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="17" t="n">
         <v>9.0</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H3" s="16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="I3" s="14" t="s">
         <v>77</v>
       </c>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
@@ -1689,6 +1695,7 @@
       <c r="I4" s="14" t="s">
         <v>81</v>
       </c>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" spans="1:9" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
@@ -2467,7 +2474,7 @@
         <v>64</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>85</v>
@@ -2488,7 +2495,7 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>87</v>
@@ -2511,7 +2518,7 @@
         <v>89</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>90</v>

--- a/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
+++ b/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="98">
   <si>
     <t>CORE-ID</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Errored</t>
+  </si>
+  <si>
+    <t>RELREC Key</t>
   </si>
   <si>
     <t>CG0001</t>
@@ -2426,7 +2429,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:I197"/>
+  <dimension ref="A1:J197"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="4" width="19.109375"/>
@@ -2438,6 +2441,7 @@
     <col min="7" max="7" bestFit="true" customWidth="true" width="12.0"/>
     <col min="8" max="8" width="12.0" customWidth="true"/>
     <col min="9" max="9" width="12.0" customWidth="true"/>
+    <col min="10" max="10" width="48.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2468,6 +2472,9 @@
       <c r="I1" s="10" t="s">
         <v>84</v>
       </c>
+      <c r="J1" s="10" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -2477,18 +2484,19 @@
         <v>72</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16" t="s">
         <v>65</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
@@ -2498,41 +2506,43 @@
         <v>76</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>68</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>72</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
@@ -3146,24 +3156,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
+++ b/lib/cumba-oss-corej-report-xlsx/src/test/resources/report/golden.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="103">
   <si>
     <t>CORE-ID</t>
   </si>
@@ -291,16 +291,31 @@
     <t>RELREC Key</t>
   </si>
   <si>
+    <t>PMDA Rule ID</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
     <t>CG0001</t>
   </si>
   <si>
     <t>SUCCESS</t>
   </si>
   <si>
+    <t>Error</t>
+  </si>
+  <si>
     <t>CG0002</t>
   </si>
   <si>
     <t>FDAB001</t>
+  </si>
+  <si>
+    <t>SD1002</t>
+  </si>
+  <si>
+    <t>Warning</t>
   </si>
   <si>
     <t>CORE-000003</t>
@@ -2429,7 +2444,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J197"/>
+  <dimension ref="A1:L197"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="4" width="19.109375"/>
@@ -2442,6 +2457,8 @@
     <col min="8" max="8" width="12.0" customWidth="true"/>
     <col min="9" max="9" width="12.0" customWidth="true"/>
     <col min="10" max="10" width="48.0" customWidth="true"/>
+    <col min="11" max="11" width="24.0" customWidth="true"/>
+    <col min="12" max="12" width="12.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2475,6 +2492,12 @@
       <c r="J1" s="10" t="s">
         <v>85</v>
       </c>
+      <c r="K1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="2" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -2484,19 +2507,25 @@
         <v>72</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="16" t="s">
         <v>65</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G2" s="15"/>
       <c r="H2" s="15"/>
       <c r="I2" s="15"/>
       <c r="J2" s="15"/>
+      <c r="K2" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="3" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
@@ -2506,43 +2535,55 @@
         <v>76</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E3" s="16" t="s">
         <v>68</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G3" s="15"/>
       <c r="H3" s="15"/>
       <c r="I3" s="15"/>
       <c r="J3" s="15"/>
+      <c r="K3" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="4" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B4" s="15" t="s">
         <v>72</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="16" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G4" s="15"/>
       <c r="H4" s="15"/>
       <c r="I4" s="15"/>
       <c r="J4" s="15"/>
+      <c r="K4" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="5" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
@@ -3156,24 +3197,24 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>7</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="15" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
